--- a/public/exports/45973328.xlsx
+++ b/public/exports/45973328.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:L25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Doktorvejen 1A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">10134911</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>3697</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Doktorvejen 1A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10134911</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>629</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ndr. Rønner 999</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">3257453</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>271</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gammel Havnevej 8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">751167, 3255182</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>1083</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Smedievejen 16</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">751172, 3254649</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>477</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnepladsen 2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">8497695</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>386</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Doktorvejen 1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">10134911</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>347</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">200020296</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-11</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Smedievejen 13</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">3254647</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>555</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">200020294</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-11</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vesterø Havnegade 28</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">3256871</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>1624</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">311564721</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-28</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byrum Hovedgade 58</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">3252675</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>4883</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">311812313</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-02-18</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byrum Hovedgade 58A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">3252675</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>284</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">311812412</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-02-18</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byrum Hovedgade 58</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">3252675</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>441</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">311812313</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-02-18</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byrum Hovedgade 58</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">3252675</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>908</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">311812313</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-02-18</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byrum Hovedgade 22A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">3253358</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>280</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">311813822</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-02-25</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Doktorvejen 1C</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">100048575</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>620</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">311814543</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 4</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">3252679</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>1676</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">311814576</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Doktorvejen 2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">3253877</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>588</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">311814547</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Doktorvejen 2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">3253877</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>292</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">311814547</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Doktorvejen 2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">3253877</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>276</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">311814547</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnepladsen 1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">8497695</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">24</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>395</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">311854222</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-08</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byrum Hovedgade 56</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">8697872</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>277</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">311854159</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-08</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byrum Hovedgade 56B</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">8697872</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>300</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">311854159</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-08</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byrum Hovedgade 56</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">8697872</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>372</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311854159</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-08</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,39 +1471,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byrum Hovedgade 56</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9940</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">8697872</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>655</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311854159</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-08</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J25"/>
+  <autoFilter ref="A1:L25"/>
 </worksheet>
 </file>
--- a/public/exports/45973328.xlsx
+++ b/public/exports/45973328.xlsx
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ndr. Rønner 999</t>
+          <t xml:space="preserve">Gammel Havnevej 8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3257453</t>
+          <t xml:space="preserve">751167, 3255182</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -230,7 +230,7 @@
         </is>
       </c>
       <c r="H4">
-        <v>271</v>
+        <v>1083</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Havnevej 8</t>
+          <t xml:space="preserve">Havnepladsen 2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">751167, 3255182</t>
+          <t xml:space="preserve">8497695</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H5">
-        <v>1083</v>
+        <v>386</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedievejen 16</t>
+          <t xml:space="preserve">Ndr. Rønner 999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,7 +341,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">751172, 3254649</t>
+          <t xml:space="preserve">3257453</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -350,7 +350,7 @@
         </is>
       </c>
       <c r="H6">
-        <v>477</v>
+        <v>271</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnepladsen 2</t>
+          <t xml:space="preserve">Smedievejen 16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">8497695</t>
+          <t xml:space="preserve">751172, 3254649</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H7">
-        <v>386</v>
+        <v>477</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byrum Hovedgade 58A</t>
+          <t xml:space="preserve">Byrum Hovedgade 58</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -706,15 +706,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H12">
-        <v>284</v>
+        <v>441</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812412</t>
+          <t xml:space="preserve">311812313</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -766,11 +766,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H13">
-        <v>441</v>
+        <v>908</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byrum Hovedgade 58</t>
+          <t xml:space="preserve">Byrum Hovedgade 58A</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -826,15 +826,15 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H14">
-        <v>908</v>
+        <v>284</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812313</t>
+          <t xml:space="preserve">311812412</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 4</t>
+          <t xml:space="preserve">Doktorvejen 2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3252679</t>
+          <t xml:space="preserve">3253877</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H17">
-        <v>1676</v>
+        <v>588</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814576</t>
+          <t xml:space="preserve">311814547</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1066,11 +1066,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H18">
-        <v>588</v>
+        <v>292</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1126,11 +1126,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H19">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doktorvejen 2</t>
+          <t xml:space="preserve">Skolevej 4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1181,20 +1181,20 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3253877</t>
+          <t xml:space="preserve">3252679</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H20">
-        <v>276</v>
+        <v>1676</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814547</t>
+          <t xml:space="preserve">311814576</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnepladsen 1</t>
+          <t xml:space="preserve">Byrum Hovedgade 56</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,20 +1241,20 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">8497695</t>
+          <t xml:space="preserve">8697872</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>395</v>
+        <v>277</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311854222</t>
+          <t xml:space="preserve">311854159</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1306,11 +1306,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H22">
-        <v>277</v>
+        <v>372</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byrum Hovedgade 56B</t>
+          <t xml:space="preserve">Byrum Hovedgade 56</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1366,11 +1366,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H23">
-        <v>300</v>
+        <v>655</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byrum Hovedgade 56</t>
+          <t xml:space="preserve">Byrum Hovedgade 56B</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1426,11 +1426,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H24">
-        <v>372</v>
+        <v>300</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byrum Hovedgade 56</t>
+          <t xml:space="preserve">Havnepladsen 1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,20 +1481,20 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8697872</t>
+          <t xml:space="preserve">8497695</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H25">
-        <v>655</v>
+        <v>395</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311854159</t>
+          <t xml:space="preserve">311854222</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">

--- a/public/exports/45973328.xlsx
+++ b/public/exports/45973328.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -479,15 +514,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-11</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -539,15 +579,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-11</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -599,15 +644,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bygningssagkyndig-NORD ApS</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-28</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -659,15 +709,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-18</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -719,15 +774,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-18</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -779,15 +839,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-18</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -839,15 +904,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-18</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-25</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-08</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-08</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-08</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-08</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,21 +1619,26 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-08</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L25"/>
+  <autoFilter ref="A1:M25"/>
 </worksheet>
 </file>